--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488148_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2488148_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4516</v>
+        <v>6.7744</v>
       </c>
       <c r="E2" t="n">
-        <v>6.6274</v>
+        <v>7.1718</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.1758</v>
+        <v>-0.3974</v>
       </c>
       <c r="G2" t="n">
         <v>4.5916</v>
@@ -610,13 +610,13 @@
         <v>3.3352</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5482</v>
+        <v>-0.2254</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.9339</v>
+        <v>-0.3895</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3857</v>
+        <v>0.1641</v>
       </c>
       <c r="V2" t="n">
         <v>-0.0005</v>
@@ -643,10 +643,10 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.7847</v>
+        <v>3.4684</v>
       </c>
       <c r="E3" t="n">
-        <v>3.4937</v>
+        <v>2.1774</v>
       </c>
       <c r="F3" t="n">
         <v>1.291</v>
@@ -688,10 +688,10 @@
         <v>0.9264</v>
       </c>
       <c r="S3" t="n">
-        <v>1.828</v>
+        <v>0.5117</v>
       </c>
       <c r="T3" t="n">
-        <v>2.0643</v>
+        <v>0.748</v>
       </c>
       <c r="U3" t="n">
         <v>-0.2363</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9995</v>
+        <v>3.2518</v>
       </c>
       <c r="E4" t="n">
-        <v>1.3951</v>
+        <v>1.3519</v>
       </c>
       <c r="F4" t="n">
-        <v>1.6044</v>
+        <v>1.8999</v>
       </c>
       <c r="G4" t="n">
         <v>3.0167</v>
@@ -766,13 +766,13 @@
         <v>2.0382</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5355</v>
+        <v>-0.2832</v>
       </c>
       <c r="T4" t="n">
-        <v>0.102</v>
+        <v>0.0588</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6375</v>
+        <v>-0.342</v>
       </c>
       <c r="V4" t="n">
         <v>1.2594</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.1755</v>
+        <v>-0.1262</v>
       </c>
       <c r="E6" t="n">
         <v>-0.0547</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.1207</v>
+        <v>-0.07149999999999999</v>
       </c>
       <c r="G6" t="n">
         <v>-0.1536</v>
@@ -922,13 +922,13 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0219</v>
+        <v>0.0274</v>
       </c>
       <c r="T6" t="n">
         <v>-0.0547</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0328</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. CARRETERO GONZALEZ</t>
+          <t>C. ALVAREZ GONZALEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2202</v>
+        <v>-0.4147</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0461</v>
+        <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2663</v>
+        <v>-0.4147</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0752</v>
+        <v>-0.4147</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.7498</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8249</v>
+        <v>-0.4147</v>
       </c>
       <c r="J7" t="n">
-        <v>0.826</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.4596</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.2856</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.7508</v>
+        <v>-0.4147</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.2901</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.4607</v>
+        <v>-0.4147</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5558999999999999</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.8529</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.297</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.5755</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.7586000000000001</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.1831</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.315</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>0.3144</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6294</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>C. ALVAREZ GONZALEZ</t>
+          <t>D. MOUHAMED KHALIFA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.4147</v>
+        <v>-0.5828</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>0.9304</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.4147</v>
+        <v>-1.5132</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.4147</v>
+        <v>-1.9363</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>0.6871</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4147</v>
+        <v>-2.6234</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.5787</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.5372</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.4147</v>
+        <v>-3.515</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>-0.8501</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4147</v>
+        <v>-2.6648</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.9264</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-0.9264</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.8529</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.5179</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-0.3513</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-0.1666</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.945</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6294</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.3155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. MOUHAMED KHALIFA</t>
+          <t>R. CARRETERO GONZALEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8279</v>
+        <v>-0.7093</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7345</v>
+        <v>-0.5414</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5625</v>
+        <v>-0.1678</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9363</v>
+        <v>0.0752</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6871</v>
+        <v>-0.7498</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.6234</v>
+        <v>0.8249</v>
       </c>
       <c r="J9" t="n">
-        <v>1.5787</v>
+        <v>0.826</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5372</v>
+        <v>-0.4596</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0415</v>
+        <v>1.2856</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.515</v>
+        <v>-0.7508</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8501</v>
+        <v>-0.2901</v>
       </c>
       <c r="O9" t="n">
-        <v>-2.6648</v>
+        <v>-0.4607</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9264</v>
+        <v>-0.5558999999999999</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9264</v>
+        <v>-1.8529</v>
       </c>
       <c r="R9" t="n">
-        <v>1.8529</v>
+        <v>1.297</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.763</v>
+        <v>0.0864</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5471</v>
+        <v>0.171</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2159</v>
+        <v>-0.08459999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>0.945</v>
+        <v>-0.315</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6294</v>
+        <v>0.3144</v>
       </c>
       <c r="X9" t="n">
-        <v>0.3155</v>
+        <v>-0.6294</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0942</v>
+        <v>-0.9657</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3522</v>
+        <v>-1.2975</v>
       </c>
       <c r="F10" t="n">
-        <v>0.258</v>
+        <v>0.3318</v>
       </c>
       <c r="G10" t="n">
         <v>-1.2193</v>
@@ -1234,13 +1234,13 @@
         <v>0.1853</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0602</v>
+        <v>0.0684</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1094</v>
+        <v>-0.0547</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0492</v>
+        <v>0.1231</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.1514</v>
+        <v>-1.1021</v>
       </c>
       <c r="E11" t="n">
         <v>-0.0688</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0826</v>
+        <v>-1.0333</v>
       </c>
       <c r="G11" t="n">
         <v>-1.0774</v>
@@ -1312,13 +1312,13 @@
         <v>0.9264</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.0555</v>
+        <v>-0.0062</v>
       </c>
       <c r="T11" t="n">
         <v>0.434</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.4895</v>
+        <v>-0.4402</v>
       </c>
       <c r="V11" t="n">
         <v>-0.945</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.7618</v>
+        <v>-1.7809</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.462</v>
+        <v>-1.4073</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2998</v>
+        <v>-0.3736</v>
       </c>
       <c r="G12" t="n">
         <v>-1.5451</v>
@@ -1390,13 +1390,13 @@
         <v>1.4823</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1251</v>
+        <v>-0.1443</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1679</v>
+        <v>-0.1131</v>
       </c>
       <c r="U12" t="n">
-        <v>0.0428</v>
+        <v>-0.0311</v>
       </c>
       <c r="V12" t="n">
         <v>-1.5738</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.7982</v>
+        <v>-2.2599</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.1802</v>
+        <v>0.4074</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.618</v>
+        <v>-2.6673</v>
       </c>
       <c r="G13" t="n">
         <v>-2.981</v>
@@ -1468,13 +1468,13 @@
         <v>3.5205</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.9257</v>
+        <v>-0.3874</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.8792</v>
+        <v>-0.2916</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.0465</v>
+        <v>-0.0958</v>
       </c>
       <c r="V13" t="n">
         <v>3.1466</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-4.1246</v>
+        <v>-3.612</v>
       </c>
       <c r="E14" t="n">
-        <v>-1.7676</v>
+        <v>-0.9841</v>
       </c>
       <c r="F14" t="n">
-        <v>-2.3571</v>
+        <v>-2.6279</v>
       </c>
       <c r="G14" t="n">
         <v>-5.6117</v>
@@ -1546,13 +1546,13 @@
         <v>2.9646</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.495</v>
+        <v>-0.9824000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-1.3132</v>
+        <v>-0.5296999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1818</v>
+        <v>-0.4527</v>
       </c>
       <c r="V14" t="n">
         <v>0.9439</v>
@@ -1579,16 +1579,16 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.933499999999998</v>
+        <v>3.2072</v>
       </c>
       <c r="E15" t="n">
-        <v>8.6775</v>
+        <v>8.951300000000002</v>
       </c>
       <c r="F15" t="n">
-        <v>-5.7441</v>
+        <v>-5.744</v>
       </c>
       <c r="G15" t="n">
-        <v>-4.2736</v>
+        <v>-4.273600000000002</v>
       </c>
       <c r="H15" t="n">
         <v>9.473500000000001</v>
@@ -1624,13 +1624,13 @@
         <v>18.5288</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1266</v>
+        <v>-1.8529</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6464999999999999</v>
+        <v>-0.3728</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.4801</v>
+        <v>-1.48</v>
       </c>
       <c r="V15" t="n">
         <v>3.775</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>12.2183</v>
+        <v>13.4438</v>
       </c>
       <c r="E16" t="n">
-        <v>15.1957</v>
+        <v>16.175</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.9774</v>
+        <v>-2.7312</v>
       </c>
       <c r="G16" t="n">
         <v>12.0807</v>
@@ -1702,13 +1702,13 @@
         <v>1.4823</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.9287</v>
+        <v>-0.7032</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.2584</v>
+        <v>-0.2791</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.6703</v>
+        <v>-0.4241</v>
       </c>
       <c r="V16" t="n">
         <v>1.5104</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.6707</v>
+        <v>3.5274</v>
       </c>
       <c r="E17" t="n">
-        <v>2.4332</v>
+        <v>3.3146</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2375</v>
+        <v>0.2128</v>
       </c>
       <c r="G17" t="n">
         <v>1.847</v>
@@ -1780,13 +1780,13 @@
         <v>0.7411</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5474</v>
+        <v>0.3093</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.4924</v>
+        <v>0.3889</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.055</v>
+        <v>-0.0796</v>
       </c>
       <c r="V17" t="n">
         <v>0.63</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ROBLES ROSADO</t>
+          <t>A. RODRIGUEZ LOPEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6042999999999999</v>
+        <v>0.9659</v>
       </c>
       <c r="E18" t="n">
-        <v>0.756</v>
+        <v>0.4534</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.1516</v>
+        <v>0.5124</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.0946</v>
+        <v>-1.1815</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4294</v>
+        <v>-0.412</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6652</v>
+        <v>-0.7695</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2215</v>
+        <v>0.6889</v>
       </c>
       <c r="K18" t="n">
-        <v>0.4207</v>
+        <v>0.4294</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6422</v>
+        <v>0.2595</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8731</v>
+        <v>-1.8704</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.8501</v>
+        <v>-0.8414</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.023</v>
+        <v>-1.029</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3706</v>
+        <v>1.8529</v>
       </c>
       <c r="Q18" t="n">
         <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3706</v>
+        <v>1.8529</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3284</v>
+        <v>-0.2726</v>
       </c>
       <c r="T18" t="n">
-        <v>0.9774</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3509</v>
+        <v>0.2773</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5671</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.3144</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.2526</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ LOPEZ</t>
+          <t>A. TEJADA CAMACHO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5747</v>
+        <v>0.2083</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.0362</v>
+        <v>0.3777</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6109</v>
+        <v>-0.1694</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.1815</v>
+        <v>2.7864</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.412</v>
+        <v>0.9661999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7695</v>
+        <v>1.8202</v>
       </c>
       <c r="J19" t="n">
-        <v>0.6889</v>
+        <v>4.0798</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4294</v>
+        <v>2.4518</v>
       </c>
       <c r="L19" t="n">
-        <v>0.2595</v>
+        <v>1.6281</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.8704</v>
+        <v>-1.2934</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.8414</v>
+        <v>-1.4855</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.029</v>
+        <v>0.1922</v>
       </c>
       <c r="P19" t="n">
-        <v>1.8529</v>
+        <v>-2.594</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-4.6322</v>
       </c>
       <c r="R19" t="n">
-        <v>1.8529</v>
+        <v>2.0382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6637999999999999</v>
+        <v>0.3926</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.0396</v>
+        <v>0.3006</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3758</v>
+        <v>0.092</v>
       </c>
       <c r="V19" t="n">
-        <v>0.5671</v>
+        <v>-0.3768</v>
       </c>
       <c r="W19" t="n">
-        <v>0.3144</v>
+        <v>0.6294</v>
       </c>
       <c r="X19" t="n">
-        <v>0.2526</v>
+        <v>-1.0062</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. TEJADA CAMACHO</t>
+          <t>J. ROBLES ROSADO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5021</v>
+        <v>-0.08169999999999999</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6715</v>
+        <v>0.1684</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1694</v>
+        <v>-0.2501</v>
       </c>
       <c r="G20" t="n">
-        <v>2.7864</v>
+        <v>-1.0946</v>
       </c>
       <c r="H20" t="n">
-        <v>0.9661999999999999</v>
+        <v>-0.4294</v>
       </c>
       <c r="I20" t="n">
-        <v>1.8202</v>
+        <v>-0.6652</v>
       </c>
       <c r="J20" t="n">
-        <v>4.0798</v>
+        <v>-0.2215</v>
       </c>
       <c r="K20" t="n">
-        <v>2.4518</v>
+        <v>0.4207</v>
       </c>
       <c r="L20" t="n">
-        <v>1.6281</v>
+        <v>-0.6422</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.2934</v>
+        <v>-0.8731</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4855</v>
+        <v>-0.8501</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1922</v>
+        <v>-0.023</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.594</v>
+        <v>0.3706</v>
       </c>
       <c r="Q20" t="n">
-        <v>-4.6322</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.0382</v>
+        <v>0.3706</v>
       </c>
       <c r="S20" t="n">
-        <v>0.6864</v>
+        <v>0.6423</v>
       </c>
       <c r="T20" t="n">
-        <v>0.5944</v>
+        <v>0.3899</v>
       </c>
       <c r="U20" t="n">
-        <v>0.092</v>
+        <v>0.2524</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.3768</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6294</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.0062</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0582</v>
+        <v>-0.6183999999999999</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.2476</v>
+        <v>-0.66</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1894</v>
+        <v>0.0417</v>
       </c>
       <c r="G21" t="n">
         <v>-0.449</v>
@@ -2092,13 +2092,13 @@
         <v>0.3706</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3683</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4377</v>
+        <v>0.1499</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0694</v>
+        <v>-0.0784</v>
       </c>
       <c r="V21" t="n">
         <v>0.315</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.1937</v>
+        <v>-1.0213</v>
       </c>
       <c r="E22" t="n">
         <v>-0.5477</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.6459</v>
+        <v>-0.4736</v>
       </c>
       <c r="G22" t="n">
         <v>0.232</v>
@@ -2170,13 +2170,13 @@
         <v>1.4823</v>
       </c>
       <c r="S22" t="n">
-        <v>0.2666</v>
+        <v>0.439</v>
       </c>
       <c r="T22" t="n">
         <v>0.2699</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0032</v>
+        <v>0.1691</v>
       </c>
       <c r="V22" t="n">
         <v>-1.3217</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.975</v>
+        <v>-2.2699</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.9546</v>
+        <v>-2.0525</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0204</v>
+        <v>-0.2174</v>
       </c>
       <c r="G23" t="n">
         <v>-1.445</v>
@@ -2248,13 +2248,13 @@
         <v>0.3706</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.2706</v>
+        <v>-0.5655</v>
       </c>
       <c r="T23" t="n">
-        <v>0.2151</v>
+        <v>0.1172</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4857</v>
+        <v>-0.6827</v>
       </c>
       <c r="V23" t="n">
         <v>-0.63</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.2119</v>
+        <v>-2.898</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6756</v>
+        <v>-2.2631</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5364</v>
+        <v>-0.6349</v>
       </c>
       <c r="G24" t="n">
         <v>-0.8484</v>
@@ -2326,13 +2326,13 @@
         <v>1.1117</v>
       </c>
       <c r="S24" t="n">
-        <v>0.9789</v>
+        <v>0.2929</v>
       </c>
       <c r="T24" t="n">
-        <v>0.485</v>
+        <v>-0.1026</v>
       </c>
       <c r="U24" t="n">
-        <v>0.4939</v>
+        <v>0.3954</v>
       </c>
       <c r="V24" t="n">
         <v>0.2516</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-2.8072</v>
+        <v>-3.4178</v>
       </c>
       <c r="E25" t="n">
-        <v>1.4715</v>
+        <v>0.5901</v>
       </c>
       <c r="F25" t="n">
-        <v>-4.2787</v>
+        <v>-4.0079</v>
       </c>
       <c r="G25" t="n">
         <v>-1.8392</v>
@@ -2404,13 +2404,13 @@
         <v>1.297</v>
       </c>
       <c r="S25" t="n">
-        <v>0.2527</v>
+        <v>-0.3578</v>
       </c>
       <c r="T25" t="n">
-        <v>0.919</v>
+        <v>0.0376</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6663</v>
+        <v>-0.3955</v>
       </c>
       <c r="V25" t="n">
         <v>-2.5177</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.5156</v>
+        <v>-4.5643</v>
       </c>
       <c r="E26" t="n">
-        <v>-3.6809</v>
+        <v>-3.7788</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.8347</v>
+        <v>-0.7855</v>
       </c>
       <c r="G26" t="n">
         <v>-4.051</v>
@@ -2482,13 +2482,13 @@
         <v>0.7411</v>
       </c>
       <c r="S26" t="n">
-        <v>0.6645</v>
+        <v>0.6159</v>
       </c>
       <c r="T26" t="n">
-        <v>0.2151</v>
+        <v>0.1172</v>
       </c>
       <c r="U26" t="n">
-        <v>0.4494</v>
+        <v>0.4986</v>
       </c>
       <c r="V26" t="n">
         <v>-0.9439</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>-5.7419</v>
+        <v>-6.2075</v>
       </c>
       <c r="E27" t="n">
-        <v>-5.6412</v>
+        <v>-6.033</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.1007</v>
+        <v>-0.1745</v>
       </c>
       <c r="G27" t="n">
         <v>-1.7639</v>
@@ -2560,13 +2560,13 @@
         <v>1.1117</v>
       </c>
       <c r="S27" t="n">
-        <v>1.7278</v>
+        <v>1.2622</v>
       </c>
       <c r="T27" t="n">
-        <v>1.0321</v>
+        <v>0.6404</v>
       </c>
       <c r="U27" t="n">
-        <v>0.6956</v>
+        <v>0.6218</v>
       </c>
       <c r="V27" t="n">
         <v>-1.2589</v>
@@ -2593,13 +2593,13 @@
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>-2.933400000000002</v>
+        <v>-2.9335</v>
       </c>
       <c r="E28" t="n">
-        <v>5.744100000000002</v>
+        <v>5.744099999999999</v>
       </c>
       <c r="F28" t="n">
-        <v>-8.6774</v>
+        <v>-8.6776</v>
       </c>
       <c r="G28" t="n">
         <v>4.2735</v>
@@ -2638,13 +2638,13 @@
         <v>12.9701</v>
       </c>
       <c r="S28" t="n">
-        <v>2.1265</v>
+        <v>2.1266</v>
       </c>
       <c r="T28" t="n">
-        <v>1.4799</v>
+        <v>1.48</v>
       </c>
       <c r="U28" t="n">
-        <v>0.6465</v>
+        <v>0.6463</v>
       </c>
       <c r="V28" t="n">
         <v>-3.7749</v>
@@ -2653,7 +2653,7 @@
         <v>3.7737</v>
       </c>
       <c r="X28" t="n">
-        <v>-7.5487</v>
+        <v>-7.548699999999999</v>
       </c>
     </row>
   </sheetData>
